--- a/NECP Scenario/Results/Regional Results/LESVOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/LESVOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.332224004071025E-08</v>
+        <v>4.906622224451032E-08</v>
       </c>
       <c r="C3">
-        <v>3.354049258106027E-08</v>
+        <v>4.936728218249449E-08</v>
       </c>
       <c r="D3">
-        <v>0.0248703842506969</v>
+        <v>0.0266415274710826</v>
       </c>
       <c r="E3">
-        <v>0.0293811295604192</v>
+        <v>0.0316585580741132</v>
       </c>
       <c r="F3">
-        <v>0.0293810970970608</v>
+        <v>0.0316585108329101</v>
       </c>
       <c r="G3">
-        <v>0.0207058368032171</v>
+        <v>0.047992979412637</v>
       </c>
       <c r="H3">
-        <v>0.0245572642370879</v>
+        <v>0.0486337274936412</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000066204</v>
+        <v>0.4000000000071798</v>
       </c>
       <c r="C13">
-        <v>0.4000000000086651</v>
+        <v>0.4000000000101808</v>
       </c>
       <c r="D13">
-        <v>0.4000000000131962</v>
+        <v>0.4000000000160451</v>
       </c>
       <c r="E13">
-        <v>0.4000000000240548</v>
+        <v>0.4000000000291761</v>
       </c>
       <c r="F13">
-        <v>0.4000000000410167</v>
+        <v>0.400000000050597</v>
       </c>
       <c r="G13">
-        <v>0.4000000000756861</v>
+        <v>0.400000000094024</v>
       </c>
       <c r="H13">
-        <v>0.4000000004231422</v>
+        <v>0.4000000005090869</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0956148675067761</v>
+        <v>0.0969309182997433</v>
       </c>
       <c r="E27">
-        <v>0.120485036500392</v>
+        <v>0.104061183543141</v>
       </c>
       <c r="F27">
-        <v>0.1508029785993663</v>
+        <v>0.1303803447079681</v>
       </c>
       <c r="G27">
-        <v>0.1790693815359981</v>
+        <v>0.1819535551676822</v>
       </c>
       <c r="H27">
-        <v>0.2226926136968551</v>
+        <v>0.2153492951046993</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3.645734855591756E-08</v>
+        <v>5.384171573519602E-08</v>
       </c>
       <c r="E29">
-        <v>2.609049334018416E-07</v>
+        <v>0.008004133225007501</v>
       </c>
       <c r="F29">
-        <v>0.0562993353341641</v>
+        <v>0.0617878450189282</v>
       </c>
       <c r="G29">
-        <v>0.0822105981878747</v>
+        <v>0.0835293179417283</v>
       </c>
       <c r="H29">
-        <v>0.0835293193737817</v>
+        <v>0.0835293194825769</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0391334439257282</v>
+        <v>0.0391442267240157</v>
       </c>
       <c r="E33">
-        <v>0.1466065446068782</v>
+        <v>0.1381981561823931</v>
       </c>
       <c r="F33">
-        <v>0.159806487673197</v>
+        <v>0.165519263269874</v>
       </c>
       <c r="G33">
-        <v>0.159806488072296</v>
+        <v>0.1655192640605304</v>
       </c>
       <c r="H33">
-        <v>0.1598064905466067</v>
+        <v>0.1655192672384683</v>
       </c>
     </row>
     <row r="34" spans="1:8">
